--- a/data/trans_dic/IP16A09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,57</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,28</t>
+          <t>0,0; 13,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,5</t>
+          <t>0,63; 6,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 23,36</t>
+          <t>4,16; 22,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,19</t>
+          <t>0,0; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 10,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 14,73</t>
+          <t>1,81; 14,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,63</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 20,6</t>
+          <t>2,18; 18,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 14,39</t>
+          <t>3,64; 14,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,77</t>
+          <t>0,65; 6,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 11,87</t>
+          <t>2,11; 11,94</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 12,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,4</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,06</t>
+          <t>1,27; 10,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,94</t>
+          <t>0,99; 8,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,49</t>
+          <t>0,75; 6,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,96</t>
+          <t>1,81; 7,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,15</t>
+          <t>0,61; 4,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,66</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,9; 5,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,6</t>
+          <t>1,38; 5,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,47; 4,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,94</t>
+          <t>1,82; 5,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,08</t>
+          <t>1,35; 4,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,14</t>
+          <t>0,72; 2,88</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3018</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5444</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3259</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5785</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2784</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3315</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3403</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3232</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3276</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>642; 6327</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3384</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4697</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2361</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3952</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1046; 5599</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4434</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3593</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>634; 5097</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4273</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>707; 6146</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2193; 8709</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>615; 5739</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1402; 7916</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3240</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3943</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4722</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>632; 5062</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>637; 5732</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>759; 6747</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8469</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9083</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2266; 9194</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1138; 8671</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>567; 5130</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1292; 7784</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2640; 10605</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>703; 6388</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4898; 14346</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5103; 15211</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2245; 8960</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Habitat-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,2</t>
+          <t>0,0; 9,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,84</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,57</t>
+          <t>0,0; 11,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,16</t>
+          <t>0,63; 6,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 22,25</t>
+          <t>4,15; 22,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,58</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 14,51</t>
+          <t>1,8; 13,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 18,99</t>
+          <t>2,2; 19,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 14,45</t>
+          <t>3,19; 13,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,06</t>
+          <t>0,65; 5,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,94</t>
+          <t>2,1; 12,21</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,62</t>
+          <t>0,0; 15,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 10,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,14</t>
+          <t>1,28; 11,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,89</t>
+          <t>1,0; 8,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,7</t>
+          <t>0,74; 6,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,34</t>
+          <t>1,9; 7,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,64</t>
+          <t>0,66; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,16</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,41</t>
+          <t>0,9; 5,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,54</t>
+          <t>1,3; 5,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,31</t>
+          <t>0,48; 4,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,33</t>
+          <t>1,79; 5,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,02</t>
+          <t>1,29; 3,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,77; 3,18</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3018</t>
+          <t>0; 3001</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 3549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5444</t>
+          <t>0; 5773</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3259</t>
+          <t>0; 3634</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5785</t>
+          <t>0; 5525</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>0; 2883</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 3745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4953</t>
+          <t>0; 5707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>0; 2869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>0; 3276</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 3713</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>642; 6327</t>
+          <t>644; 6410</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3384</t>
+          <t>0; 3150</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1046; 5599</t>
+          <t>1043; 5681</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4434</t>
+          <t>0; 4241</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3593</t>
+          <t>0; 3997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>634; 5097</t>
+          <t>634; 4777</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4273</t>
+          <t>0; 3832</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>707; 6146</t>
+          <t>713; 6316</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2193; 8709</t>
+          <t>1922; 8372</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>615; 5739</t>
+          <t>619; 5532</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1402; 7916</t>
+          <t>1391; 8098</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>0; 3950</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3943</t>
+          <t>0; 3537</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>632; 5062</t>
+          <t>638; 5653</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>637; 5732</t>
+          <t>646; 5473</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>759; 6747</t>
+          <t>747; 6832</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2266; 9194</t>
+          <t>2376; 9439</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1138; 8671</t>
+          <t>1233; 7573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>567; 5130</t>
+          <t>570; 5852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1292; 7784</t>
+          <t>1288; 7196</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2640; 10605</t>
+          <t>2493; 10500</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>703; 6388</t>
+          <t>707; 7017</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4898; 14346</t>
+          <t>4821; 13572</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5103; 15211</t>
+          <t>4866; 14812</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2245; 8960</t>
+          <t>2391; 9879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,28</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,07</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 10,57</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,67</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,74</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,06%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,03</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,24</t>
+          <t>0,63; 6,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 22,58</t>
+          <t>1,81; 14,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 8,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>2,21; 20,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 13,6</t>
+          <t>3,99; 23,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 9,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 19,51</t>
+          <t>0,0; 11,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,89</t>
+          <t>3,83; 14,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,84</t>
+          <t>0,65; 5,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,21</t>
+          <t>2,13; 11,87</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,38</t>
+          <t>0,0; 10,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>1,29; 11,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,57</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,32</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,49</t>
+          <t>1,01; 8,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,78</t>
+          <t>0,7; 6,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,53</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,05</t>
+          <t>1,36; 5,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,6</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,0</t>
+          <t>2,02; 7,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,48</t>
+          <t>0,68; 4,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,74</t>
+          <t>0,35; 3,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,04</t>
+          <t>1,69; 4,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,91</t>
+          <t>1,35; 4,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,18</t>
+          <t>0,74; 3,14</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>560</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 5226</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3549</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 3468</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5773</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2397</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3634</t>
+          <t>0; 3041</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5525</t>
+          <t>0; 6448</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2883</t>
+          <t>0; 2897</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3745</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5707</t>
+          <t>0; 3389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2869</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3778</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 4861</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2860</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3713</t>
+          <t>0; 3711</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>644; 6410</t>
+          <t>645; 6671</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3150</t>
+          <t>0; 3351</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2760</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1126</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1153</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1043; 5681</t>
+          <t>636; 5175</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4241</t>
+          <t>0; 4422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3997</t>
+          <t>714; 6668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>634; 4777</t>
+          <t>1005; 5877</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3832</t>
+          <t>0; 3990</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>713; 6316</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1922; 8372</t>
+          <t>2308; 8675</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>619; 5532</t>
+          <t>613; 5464</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1391; 8098</t>
+          <t>1414; 7875</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>787</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3950</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>645; 5524</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>638; 5653</t>
+          <t>0; 3560</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>646; 5473</t>
+          <t>654; 5766</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>747; 6832</t>
+          <t>710; 6534</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2277</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2376; 9439</t>
+          <t>1282; 7416</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1233; 7573</t>
+          <t>2611; 10721</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>570; 5852</t>
+          <t>705; 6921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1288; 7196</t>
+          <t>2528; 9976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2493; 10500</t>
+          <t>1267; 7769</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>707; 7017</t>
+          <t>571; 5948</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4821; 13572</t>
+          <t>4546; 13313</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4866; 14812</t>
+          <t>5106; 15444</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2391; 9879</t>
+          <t>2305; 9767</t>
         </is>
       </c>
     </row>
